--- a/2022 data/excel_outputs/403_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/403_boothwise_data.xlsx
@@ -14,9 +14,78 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="263">
   <si>
     <t>AC 403 Booth-wise Data</t>
+  </si>
+  <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
   </si>
   <si>
     <t>BOOTH ID</t>
@@ -25,652 +94,652 @@
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>#### ####0 ##0 ###### ######## #### #### ##0.1</t>
+    <t>DADADADA DADADADA0 DADA0 DADADADADADA DADADADADADADADA DADADADA DADADADA DADA0.1</t>
   </si>
   <si>
-    <t>#### ####0 ##0 ###### ######## #### #### ##0.2</t>
+    <t>DADADADA DADADADA0 DADA0 DADADADADADA DADADADADADADADA DADADADA DADADADA DADA0.2</t>
   </si>
   <si>
-    <t>####0##0 #### ######## ;###0##0ddh</t>
+    <t>DADADADA0DADA0 DADADADA DADADADADADADADA ;DADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0##0 #### ######## ;#0##0ddh</t>
+    <t>DADADADA0DADA0 DADADADA DADADADADADADADA ;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>##0##0##0 #########e #0##0.#</t>
+    <t>DADA0DADA0DADA0 DADADADADADADADADAE DA0DADA0.DA</t>
   </si>
   <si>
-    <t>####0##0######### ;### ###ddhe #0##0.#</t>
+    <t>DADADADA0DADA0DADADADADADADADADA ;DADADA DADADADDHAE DA0DADA0.DA</t>
   </si>
   <si>
-    <t>##0#0##0 ######## ##### ##### #########e #0##0.#</t>
+    <t>DADA0DA0DADA0 DADADADADADADADA DADADADADA DADADADADA DADADADADADADADADAE DA0DADA0.DA</t>
   </si>
   <si>
-    <t>##0#0##0 ######## ##### ##### ######### #0##0.#</t>
+    <t>DADA0DA0DADA0 DADADADADADADADA DADADADADA DADADADADA DADADADADADADADADA DA0DADA0.DA</t>
   </si>
   <si>
-    <t>########## ######## ######## #0 ###.#</t>
+    <t>DADADADADADADADADADA DADADADADADADADA DADADADADADADADA DA0 DADADA.DA</t>
   </si>
   <si>
-    <t>########## ######## ######## #0 ##0 #</t>
+    <t>DADADADADADADADADADA DADADADADADADADA DADADADADADADADA DA0 DADA0 DA</t>
   </si>
   <si>
-    <t>### #### ### ##### ######## #nn#nn#</t>
+    <t>DADADA DADADADA DADADA DADADADADA DADADADADADADADA DANDANDA</t>
   </si>
   <si>
-    <t>####0##0###### #### ;#0##0ddh</t>
+    <t>DADADADA0DADA0DADADADADADA DADADADA ;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0 ##### ####.#</t>
+    <t>DADADADA0 DADA0 DADADADADA DADADADA.DA</t>
   </si>
   <si>
-    <t>#### ####0##0 ####### ##### #### ##0.1</t>
+    <t>DADADADA DADADADA0DADA0 DADADADADADADA DADADADADA DADADADA DADA0.1</t>
   </si>
   <si>
-    <t>####0##0 ######### ;###0##0ddh</t>
+    <t>DADADADA0DADA0 DADADADADADADADADA ;DADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0##0 ######### ;####0##0ddh</t>
+    <t>DADADADA0DADA0 DADADADADADADADADA ;DADADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0##0###### ##### ##### #####;###0##0ddh</t>
+    <t>DADADADA0DADA0DADADADADADA DADADADADA DADADADADA DADADADADA;DADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0##0###### ##### ##### #####;####0##0ddh</t>
+    <t>DADADADA0DADA0DADADADADADA DADADADADA DADADADADA DADADADADA;DADADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0 ###### ##### #####.######;###0##0ddh</t>
+    <t>DADADADA0 DADA0 DADADADADADA DADADADADA DADADADADA.DADADADADADA;DADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0 ###### ##### #####.######;####0##0ddh</t>
+    <t>DADADADA0 DADA0 DADADADADADA DADADADADA DADADADADA.DADADADADADA;DADADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0##0#### #########e #### ##0.#</t>
+    <t>DADADADA0DADA0DADADADA DADADADADADADADADAE DADADADA DADA0.DA</t>
   </si>
   <si>
-    <t>####0##0 #### ######### #### ##0.#</t>
+    <t>DADADADA0DADA0 DADADADA DADADADADADADADADA DADADADA DADA0.DA</t>
   </si>
   <si>
-    <t>####0 ##0#### ######### #### ##0.#</t>
+    <t>DADADADA0 DADA0DADADADA DADADADADADADADADA DADADADA DADA0.DA</t>
   </si>
   <si>
-    <t>####0 ##0#######</t>
+    <t>DADADADA0 DADA0DADADADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0 ####### ;#0##0ddh</t>
+    <t>DADADADA0 DADA0 DADADADADADADA ;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0####### ;#0##0ddh</t>
+    <t>DADADADA0 DADA0DADADADADADADA ;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>#### ##### ######## #### ##0 01 ########</t>
+    <t>DADADADA DADADADADA DADADADADADADADA DADADADA DADA0 01 DADADADADADADADA</t>
   </si>
   <si>
-    <t>#### ##### ######## #### ##0 02 ########</t>
+    <t>DADADADA DADADADADA DADADADADADADADA DADADADA DADA0 02 DADADADADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0 ###### #### ##0.1</t>
+    <t>DADADADA0 DADA0 DADADADADADA DADADADA DADA0.1</t>
   </si>
   <si>
-    <t>####0 ##0 ###### #### ##0.2</t>
+    <t>DADADADA0 DADA0 DADADADADADA DADADADA DADA0.2</t>
   </si>
   <si>
-    <t>##### ########### ##0 ##0 ##0 ########;#0##0ddh</t>
+    <t>DADADADADA DADADADADADADADADADADA DADA0 DADA0 DADA0 DADADADADADADADA;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0 ######</t>
+    <t>DADADADA0 DADA0 DADADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0#### ####### ;#0##0ddh</t>
+    <t>DADADADA0 DADA0DADADADA DADADADADADADA ;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0 #### #######;#0##0ddh</t>
+    <t>DADADADA0 DADA0 DADADADA DADADADADADADA;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>#### ### ##0##0 ##0 #####</t>
+    <t>DADADADA DADADA DADA0DADA0 DADA0 DADADADADA</t>
   </si>
   <si>
-    <t>####0##0 #####</t>
+    <t>DADADADA0DADA0 DADADADADA</t>
   </si>
   <si>
-    <t>### ### ####0 ##0########e #0##0.#</t>
+    <t>DADADA DADADA DADADADA0 DADA0DADADADADADADADAE DA0DADA0.DA</t>
   </si>
   <si>
-    <t>####0 ##0############ #####</t>
+    <t>DADADADA0 DADA0DADADADADADADADADADADADA DADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0######## #### ###### #### #0.1</t>
+    <t>DADADADA0 DADA0DADADADADADADADA DADADADA DADADADADADA DADADADA DA0.1</t>
   </si>
   <si>
-    <t>####0 ##0######## #### ###### #### #0.2</t>
+    <t>DADADADA0 DADA0DADADADADADADADA DADADADA DADADADADADA DADADADA DA0.2</t>
   </si>
   <si>
-    <t>####0 ##0########</t>
+    <t>DADADADA0 DADA0DADADADADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0 ####</t>
+    <t>DADADADA0 DADA0 DADADADA</t>
   </si>
   <si>
-    <t>####0 ##0 #####;#0##0ddh</t>
+    <t>DADADADA0 DADA0 DADADADADA;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0##### ;#0##0ddh</t>
+    <t>DADADADA0 DADA0DADADADADA ;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>##### ##0##0 ####### #### ##0.1</t>
+    <t>DADADADADA DADA0DADA0 DADADADADADADA DADADADA DADA0.1</t>
   </si>
   <si>
-    <t>##### ##0##0 ####### #### ##0.2</t>
+    <t>DADADADADA DADA0DADA0 DADADADADADADA DADADADA DADA0.2</t>
   </si>
   <si>
-    <t>####0 ##0######</t>
+    <t>DADADADA0 DADA0DADADADADADA</t>
   </si>
   <si>
-    <t>##0##0######### ###### #0##0.#</t>
+    <t>DADA0DADA0DADADADADADADADADA DADADADADADA DA0DADA0.DA</t>
   </si>
   <si>
-    <t>##0##0 ######### ###### #0##0.#</t>
+    <t>DADA0DADA0 DADADADADADADADADA DADADADADADA DA0DADA0.DA</t>
   </si>
   <si>
-    <t>##0##0 ######### ######e #0##0.#</t>
+    <t>DADA0DADA0 DADADADADADADADADA DADADADADADAE DA0DADA0.DA</t>
   </si>
   <si>
-    <t>##0#0##0###### ###### ##### ###### ### ######;###0##0ddh</t>
+    <t>DADA0DA0DADA0DADADADADADA DADADADADADA DADADADADA DADADADADADA DADADA DADADADADADA;DADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>##0#0##0###### ###### ##### ###### ### ######;####0##0ddh</t>
+    <t>DADA0DA0DADA0DADADADADADA DADADADADADA DADADADADA DADADADADADA DADADA DADADADADADA;DADADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>######### ####### ####</t>
+    <t>DADADADADADADADADA DADADADADADADA DADADADA</t>
   </si>
   <si>
-    <t>####0 ##0 #### ;#0##0ddh</t>
+    <t>DADADADA0 DADA0 DADADADA ;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>##0##0##0####</t>
+    <t>DADA0DADA0DADA0DADADADA</t>
   </si>
   <si>
-    <t>####0##0 #####e #0##0.#</t>
+    <t>DADADADA0DADA0 DADADADADAE DA0DADA0.DA</t>
   </si>
   <si>
-    <t>####0 ##0 #####e #0##0.#</t>
+    <t>DADADADA0 DADA0 DADADADADAE DA0DADA0.DA</t>
   </si>
   <si>
-    <t>####0##0#######</t>
+    <t>DADADADA0DADA0DADADADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0 #### #0##0.#</t>
+    <t>DADADADA0 DADA0 DADADADA DA0DADA0.DA</t>
   </si>
   <si>
-    <t>##0 ##0 ##0 ####### ### ###e #0##0.#</t>
+    <t>DADA0 DADA0 DADA0 DADADADADADADA DADADA DADADAE DA0DADA0.DA</t>
   </si>
   <si>
-    <t>####0 ##0 #######</t>
+    <t>DADADADA0 DADA0 DADADADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0 ####### #### ##0.1</t>
+    <t>DADADADA0 DADA0 DADADADADADADA DADADADA DADA0.1</t>
   </si>
   <si>
-    <t>####0 ##0 ####### #### ##0.2</t>
+    <t>DADADADA0 DADA0 DADADADADADADA DADADADA DADA0.2</t>
   </si>
   <si>
-    <t>####0 ##0 ##### #######</t>
+    <t>DADADADA0 DADA0 DADADADADA DADADADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0 ##### #####</t>
+    <t>DADADADA0 DADA0 DADADADADA DADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0 #### #####</t>
+    <t>DADADADA0 DADA0 DADADADA DADADADADA</t>
   </si>
   <si>
-    <t>######## ######## #########</t>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0 ########</t>
+    <t>DADADADA0 DADA0 DADADADADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0 ##########</t>
+    <t>DADADADA0 DADA0 DADADADADADADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0 ######## #### ##0.1</t>
+    <t>DADADADA0 DADA0 DADADADADADADADA DADADADA DADA0.1</t>
   </si>
   <si>
-    <t>####0 ##0 ######## #### ##0.2</t>
+    <t>DADADADA0 DADA0 DADADADADADADADA DADADADA DADA0.2</t>
   </si>
   <si>
-    <t>####0##0 #### #### ##0.1</t>
+    <t>DADADADA0DADA0 DADADADA DADADADA DADA0.1</t>
   </si>
   <si>
-    <t>####0##0 #### #### ##0.2</t>
+    <t>DADADADA0DADA0 DADADADA DADADADA DADA0.2</t>
   </si>
   <si>
-    <t>####0##0 ####### #### ######## ####</t>
+    <t>DADADADA0DADA0 DADADADADADADA DADADADA DADADADADADADADA DADADADA</t>
   </si>
   <si>
-    <t>####0##0 #### #######</t>
+    <t>DADADADA0DADA0 DADADADA DADADADADADADA</t>
   </si>
   <si>
-    <t>##### ######## ######## ####</t>
+    <t>DADADADADA DADADADADADADADA DADADADADADADADA DADADADA</t>
   </si>
   <si>
-    <t>##0 ##0 ##0 ########;###0##0ddh</t>
+    <t>DADA0 DADA0 DADA0 DADADADADADADADA;DADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>##0 ##0 ##0 ########;####0##0ddh</t>
+    <t>DADA0 DADA0 DADA0 DADADADADADADADA;DADADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0 #### ### ######</t>
+    <t>DADADADA0 DADA0 DADADADA DADADA DADADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0####;#0##0ddh</t>
+    <t>DADADADA0 DADA0DADADADA;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0## ######</t>
+    <t>DADADADA0DADA DADADADADADA</t>
   </si>
   <si>
-    <t>####0##0###### ##### ##### ########;###0##0ddh</t>
+    <t>DADADADA0DADA0DADADADADADA DADADADADA DADADADADA DADADADADADADADA;DADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0##0###### ##### ##### ########;####0##0ddh</t>
+    <t>DADADADA0DADA0DADADADADADA DADADADADA DADADADADA DADADADADADADADA;DADADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>##### ##0 ##0 ########e #### ######.1</t>
+    <t>DADADADADA DADA0 DADA0 DADADADADADADADAE DADADADA DADADADADADA.1</t>
   </si>
   <si>
-    <t>##### ##0 ##0 ########e #### ######.2</t>
+    <t>DADADADADA DADA0 DADA0 DADADADADADADADAE DADADADA DADADADADADA.2</t>
   </si>
   <si>
-    <t>##### ##0 ##0 ########e #### ######.3</t>
+    <t>DADADADADA DADA0 DADA0 DADADADADADADADAE DADADADA DADADADADADA.3</t>
   </si>
   <si>
-    <t>##0##0##0#######;###0##0ddh</t>
+    <t>DADA0DADA0DADA0DADADADADADADA;DADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>##0##0##0#######;####0##0ddh</t>
+    <t>DADA0DADA0DADA0DADADADADADADA;DADADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0 #####</t>
+    <t>DADADADA0 DADA0 DADADADADA</t>
   </si>
   <si>
-    <t>####0##0 ##########</t>
+    <t>DADADADA0DADA0 DADADADADADADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0 ##### #### ######.#</t>
+    <t>DADADADA0 DADA0 DADADADADA DADADADA DADADADADADA.DA</t>
   </si>
   <si>
-    <t>####0 ##0 ##### #### ######.2</t>
+    <t>DADADADA0 DADA0 DADADADADA DADADADA DADADADADADA.2</t>
   </si>
   <si>
-    <t>####0##0######## #### ####e #### ######.#</t>
+    <t>DADADADA0DADA0DADADADADADADADA DADADADA DADADADAE DADADADA DADADADADADA.DA</t>
   </si>
   <si>
-    <t>##0 ##0 ##0########e #0##0.#</t>
+    <t>DADA0 DADA0 DADA0DADADADADADADADAE DA0DADA0.DA</t>
   </si>
   <si>
-    <t>####0 ##0#### ;########ddh</t>
+    <t>DADADADA0 DADA0DADADADA ;DADADADADADADADADDHA</t>
   </si>
   <si>
-    <t>####0##0#### ### ######e #0##0.#</t>
+    <t>DADADADA0DADA0DADADADA DADADA DADADADADADAE DA0DADA0.DA</t>
   </si>
   <si>
-    <t>#### ####0##0 ######e #0##0.1</t>
+    <t>DADADADA DADADADA0DADA0 DADADADADADAE DA0DADA0.1</t>
   </si>
   <si>
-    <t>#### ####0##0 ######e #0##0.2</t>
+    <t>DADADADA DADADADA0DADA0 DADADADADADAE DA0DADA0.2</t>
   </si>
   <si>
-    <t>####0##0 ##### #0##0.#</t>
+    <t>DADADADA0DADA0 DADADADADA DA0DADA0.DA</t>
   </si>
   <si>
-    <t>####0##0 #######</t>
+    <t>DADADADA0DADA0 DADADADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0 ##### #### ##0.1</t>
+    <t>DADADADA0 DADA0 DADADADADA DADADADA DADA0.1</t>
   </si>
   <si>
-    <t>####0 ##0 ##### #### ##0.2</t>
+    <t>DADADADA0 DADA0 DADADADADA DADADADA DADA0.2</t>
   </si>
   <si>
-    <t>####0 ##0#### #### ##0.1</t>
+    <t>DADADADA0 DADA0DADADADA DADADADA DADA0.1</t>
   </si>
   <si>
-    <t>####0 ##0#### #### ##0.2</t>
+    <t>DADADADA0 DADA0DADADADA DADADADA DADA0.2</t>
   </si>
   <si>
-    <t>####0 ##0#### #### ##0.3</t>
+    <t>DADADADA0 DADA0DADADADA DADADADA DADA0.3</t>
   </si>
   <si>
-    <t>##0#0######## ####e #0##0.#</t>
+    <t>DADA0DA0DADADADADADADADA DADADADAE DA0DADA0.DA</t>
   </si>
   <si>
-    <t>##0#0######## #### #0##0.#</t>
+    <t>DADA0DA0DADADADADADADADA DADADADA DA0DADA0.DA</t>
   </si>
   <si>
-    <t>##0#0######## #### #0##0.4</t>
+    <t>DADA0DA0DADADADADADADADA DADADADA DA0DADA0.4</t>
   </si>
   <si>
-    <t>####0 ##0 ####e #######e #0##0.#</t>
+    <t>DADADADA0 DADA0 DADADADAE DADADADADADADAE DA0DADA0.DA</t>
   </si>
   <si>
-    <t>####0 ##0 ####e #######e #0##0.4</t>
+    <t>DADADADA0 DADA0 DADADADAE DADADADADADADAE DA0DADA0.4</t>
   </si>
   <si>
-    <t>####0 ##0 ######;###0##0ddh</t>
+    <t>DADADADA0 DADA0 DADADADADADA;DADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0 ######;####0##0ddh</t>
+    <t>DADADADA0 DADA0 DADADADADADA;DADADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0##0######## #### ##0.1</t>
+    <t>DADADADA0DADA0DADADADADADADADA DADADADA DADA0.1</t>
   </si>
   <si>
-    <t>####0##0######## #### ##0.2</t>
+    <t>DADADADA0DADA0DADADADADADADADA DADADADA DADA0.2</t>
   </si>
   <si>
-    <t>####0##0######</t>
+    <t>DADADADA0DADA0DADADADADADA</t>
   </si>
   <si>
-    <t>####0##0 #######e #0##0.1</t>
+    <t>DADADADA0DADA0 DADADADADADADAE DA0DADA0.1</t>
   </si>
   <si>
-    <t>####0##0 #######e #0##0.2</t>
+    <t>DADADADA0DADA0 DADADADADADADAE DA0DADA0.2</t>
   </si>
   <si>
-    <t>####0##0 #######e #0##0.3</t>
+    <t>DADADADA0DADA0 DADADADADADADAE DA0DADA0.3</t>
   </si>
   <si>
-    <t>####0##0 ######e #0##0.#</t>
+    <t>DADADADA0DADA0 DADADADADADAE DA0DADA0.DA</t>
   </si>
   <si>
-    <t>####0 ##0 ##### ;#0##0ddh</t>
+    <t>DADADADA0 DADA0 DADADADADA ;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0 ######## ;###0##0ddh</t>
+    <t>DADADADA0 DADA0 DADADADADADADADA ;DADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0 ######## ;####0##0ddh</t>
+    <t>DADADADA0 DADA0 DADADADADADADADA ;DADADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0###### ####.#</t>
+    <t>DADADADA0 DADA0DADADADADADA DADADADA.DA</t>
   </si>
   <si>
-    <t>####0##0####### ##### #######</t>
+    <t>DADADADA0DADA0DADADADADADADA DADADADADA DADADADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0 ####### ####</t>
+    <t>DADADADA0 DADA0 DADADADADADADA DADADADA</t>
   </si>
   <si>
-    <t>####0##0 ######### ;#####ddh ;#0##0ddh</t>
+    <t>DADADADA0DADA0 DADADADADADADADADA ;DADADADADADDHA ;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0##### #### ##0.1</t>
+    <t>DADADADA0 DADA0DADADADADA DADADADA DADA0.1</t>
   </si>
   <si>
-    <t>####0 ##0##### #### ##0.2</t>
+    <t>DADADADA0 DADA0DADADADADA DADADADA DADA0.2</t>
   </si>
   <si>
-    <t>####0 ##0 ####e ####.#</t>
+    <t>DADADADA0 DADA0 DADADADAE DADADADA.DA</t>
   </si>
   <si>
-    <t>####0 ##0 #### #### ##0.1</t>
+    <t>DADADADA0 DADA0 DADADADA DADADADA DADA0.1</t>
   </si>
   <si>
-    <t>####0 ##0 #### #### ##0.2</t>
+    <t>DADADADA0 DADA0 DADADADA DADADADA DADA0.2</t>
   </si>
   <si>
-    <t>####0##0 ##### ;#0##0ddh</t>
+    <t>DADADADA0DADA0 DADADADADA ;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0##### ####.#</t>
+    <t>DADADADA0 DADA0DADADADADA DADADADA.DA</t>
   </si>
   <si>
-    <t>####0##0 ########e #0##0.#</t>
+    <t>DADADADA0DADA0 DADADADADADADADAE DA0DADA0.DA</t>
   </si>
   <si>
-    <t>####0 ##0 #########</t>
+    <t>DADADADA0 DADA0 DADADADADADADADADA</t>
   </si>
   <si>
-    <t>#### ####0##0 ######</t>
+    <t>DADADADA DADADADA0DADA0 DADADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0 #####;###0##0ddh</t>
+    <t>DADADADA0 DADA0 DADADADADA;DADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0 #####;####0##0ddh</t>
+    <t>DADADADA0 DADA0 DADADADADA;DADADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0 ##### ;##0##0ddh</t>
+    <t>DADADADA0 DADA0 DADADADADA ;DADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0 ###### ######</t>
+    <t>DADADADA0 DADA0 DADADADADADA DADADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0######e ####.#</t>
+    <t>DADADADA0 DADA0DADADADADADAE DADADADA.DA</t>
   </si>
   <si>
-    <t>####0 ##0 ##### ##### ##### ######</t>
+    <t>DADADADA0 DADA0 DADADADADA DADADADADA DADADADADA DADADADADADA</t>
   </si>
   <si>
-    <t>##### ##0 ######## #####</t>
+    <t>DADADADADA DADA0 DADADADADADADADA DADADADADA</t>
   </si>
   <si>
-    <t>####0##0#######e ####.#</t>
+    <t>DADADADA0DADA0DADADADADADADAE DADADADA.DA</t>
   </si>
   <si>
-    <t>####0##0#######e ####.3</t>
+    <t>DADADADA0DADA0DADADADADADADAE DADADADA.3</t>
   </si>
   <si>
-    <t>####0 ##0#### ### #####e #0##0.#</t>
+    <t>DADADADA0 DADA0DADADADA DADADA DADADADADAE DA0DADA0.DA</t>
   </si>
   <si>
-    <t>####0 ##0 #### ### #####e #0##0.#</t>
+    <t>DADADADA0 DADA0 DADADADA DADADA DADADADADAE DA0DADA0.DA</t>
   </si>
   <si>
-    <t>##0##0##0##### #### ##0.1</t>
+    <t>DADA0DADA0DADA0DADADADADA DADADADA DADA0.1</t>
   </si>
   <si>
-    <t>##0##0##0##### #### ##0.2</t>
+    <t>DADA0DADA0DADA0DADADADADA DADADADA DADA0.2</t>
   </si>
   <si>
-    <t>##0##0##0##### #### ##0.3</t>
+    <t>DADA0DADA0DADA0DADADADADA DADADADA DADA0.3</t>
   </si>
   <si>
-    <t>####0##0##### ;#0##0ddh</t>
+    <t>DADADADA0DADA0DADADADADA ;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0##0#####;#0##0ddh</t>
+    <t>DADADADA0DADA0DADADADADA;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0##0#########</t>
+    <t>DADADADA0DADA0DADADADADADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0######## ;##0##0ddh</t>
+    <t>DADADADA0 DADA0DADADADADADADADA ;DADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0 ######## ;#0##0ddh</t>
+    <t>DADADADA0 DADA0 DADADADADADADADA ;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0##0###### #### ##### #####</t>
+    <t>DADADADA0DADA0DADADADADADA DADADADA DADADADADA DADADADADA</t>
   </si>
   <si>
-    <t>####0##0 ###### ;##0##0ddh</t>
+    <t>DADADADA0DADA0 DADADADADADA ;DADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0##0 ###### ;#0##0ddh</t>
+    <t>DADADADA0DADA0 DADADADADADA ;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>##0##0##0 #####</t>
+    <t>DADA0DADA0DADA0 DADADADADA</t>
   </si>
   <si>
-    <t>##0##0##0 ##### ;####0##0ddh</t>
+    <t>DADA0DADA0DADA0 DADADADADA ;DADADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0#####e ####.#</t>
+    <t>DADADADA0 DADA0DADADADADAE DADADADA.DA</t>
   </si>
   <si>
-    <t>####0##0 ####</t>
+    <t>DADADADA0DADA0 DADADADA</t>
   </si>
   <si>
-    <t>####0 ##0 ######## ####.#</t>
+    <t>DADADADA0 DADA0 DADADADADADADADA DADADADA.DA</t>
   </si>
   <si>
-    <t>####0 ##0######### ;#0##0ddh</t>
+    <t>DADADADA0 DADA0DADADADADADADADADA ;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0##0#########;#0##0ddh</t>
+    <t>DADADADA0DADA0DADADADADADADADADA;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0########## ####.1</t>
+    <t>DADADADA0 DADA0DADADADADADADADADADA DADADADA.1</t>
   </si>
   <si>
-    <t>####0 ##0########## ####.2</t>
+    <t>DADADADA0 DADA0DADADADADADADADADADA DADADADA.2</t>
   </si>
   <si>
-    <t>####0 ##0##### #### ###.1</t>
+    <t>DADADADA0 DADA0DADADADADA DADADADA DADADA.1</t>
   </si>
   <si>
-    <t>####0 ##0##### #### ###.2</t>
+    <t>DADADADA0 DADA0DADADADADA DADADADA DADADA.2</t>
   </si>
   <si>
-    <t>####0 ##0##### #### ###.3</t>
+    <t>DADADADA0 DADA0DADADADADA DADADADA DADADA.3</t>
   </si>
   <si>
-    <t>####0 ##0##### ;##0##0ddh</t>
+    <t>DADADADA0 DADA0DADADADADA ;DADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0##### ;######## ####ddh</t>
+    <t>DADADADA0 DADA0DADADADADA ;DADADADADADADADA DADADADADDHA</t>
   </si>
   <si>
-    <t>####0 ##0 ####;###0##0ddh</t>
+    <t>DADADADA0 DADA0 DADADADA;DADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0 ####;####0##0ddh</t>
+    <t>DADADADA0 DADA0 DADADADA;DADADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0#########</t>
+    <t>DADADADA0 DADA0DADADADADADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0 ###### ;#0##0ddh</t>
+    <t>DADADADA0 DADA0 DADADADADADA ;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0###### ;#0##0ddh</t>
+    <t>DADADADA0 DADA0DADADADADADA ;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0###### ;##0##0ddh</t>
+    <t>DADADADA0 DADA0DADADADADADA ;DADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>##0 ##0 ##0###### #### ##0.1</t>
+    <t>DADA0 DADA0 DADA0DADADADADADA DADADADA DADA0.1</t>
   </si>
   <si>
-    <t>##0 ##0 ##0###### #### ##0.2</t>
+    <t>DADA0 DADA0 DADA0DADADADADADA DADADADA DADA0.2</t>
   </si>
   <si>
-    <t>##0 ##0 ##0###### #### ##0.3</t>
+    <t>DADA0 DADA0 DADA0DADADADADADA DADADADA DADA0.3</t>
   </si>
   <si>
-    <t>###### ##### ##### ##### ######e ####.#</t>
+    <t>DADADADADADA DADADADADA DADADADADA DADADADADA DADADADADADAE DADADADA.DA</t>
   </si>
   <si>
-    <t>###### ##### ##### ##### ######e ####.4</t>
+    <t>DADADADADADA DADADADADA DADADADADA DADADADADA DADADADADADAE DADADADA.4</t>
   </si>
   <si>
-    <t>####0 ##0 #######;###0##0ddh</t>
+    <t>DADADADA0 DADA0 DADADADADADADA;DADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0 #######;####0##0ddh</t>
+    <t>DADADADA0 DADA0 DADADADADADADA;DADADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0#### ####.#</t>
+    <t>DADADADA0 DADA0DADADADA DADADADA.DA</t>
   </si>
   <si>
-    <t>#0####0##0 #### #### ##0.1</t>
+    <t>DA0DADADADA0DADA0 DADADADA DADADADA DADA0.1</t>
   </si>
   <si>
-    <t>#0####0##0 #### #### ##0.2</t>
+    <t>DA0DADADADA0DADA0 DADADADA DADADADA DADA0.2</t>
   </si>
   <si>
-    <t>###### ##### ####0 ##0#### ;##0##0ddh</t>
+    <t>DADADADADADA DADADADADA DADADADA0 DADA0DADADADA ;DADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>###### ##### ####0##0#### ;#0##0ddh</t>
+    <t>DADADADADADA DADADADADA DADADADA0DADA0DADADADA ;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>###### ##### ####0 ##0#### ;#0##0ddh</t>
+    <t>DADADADADADA DADADADADA DADADADA0 DADA0DADADADA ;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>#### ####0 ##0####### #### ##0.1</t>
+    <t>DADADADA DADADADA0 DADA0DADADADADADADA DADADADA DADA0.1</t>
   </si>
   <si>
-    <t>#### ####0 ##0####### #### ##0.2</t>
+    <t>DADADADA DADADADA0 DADA0DADADADADADADA DADADADA DADA0.2</t>
   </si>
   <si>
-    <t>#### ####0 ##0####### #### ##0.3</t>
+    <t>DADADADA DADADADA0 DADA0DADADADADADADA DADADADA DADA0.3</t>
   </si>
   <si>
-    <t>####0 ##0###### ##### ######</t>
+    <t>DADADADA0 DADA0DADADADADADA DADADADADA DADADADADADA</t>
   </si>
   <si>
-    <t>####0##0 ##### ##### ##### ######</t>
+    <t>DADADADA0DADA0 DADADADADA DADADADADA DADADADADA DADADADADADA</t>
   </si>
   <si>
-    <t>##0 ##0 ##0##### ##### ##### #####e ####.#</t>
+    <t>DADA0 DADA0 DADA0DADADADADA DADADADADA DADADADADA DADADADADAE DADADADA.DA</t>
   </si>
   <si>
-    <t>####0 ##0 ######e ####.#</t>
+    <t>DADADADA0 DADA0 DADADADADADAE DADADADA.DA</t>
   </si>
   <si>
-    <t>####0 ##0####### ;##0##0ddh</t>
+    <t>DADADADA0 DADA0DADADADADADADA ;DADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0######## ;#0##0ddh</t>
+    <t>DADADADA0 DADA0DADADADADADADADA ;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0######### ;##0##0ddh</t>
+    <t>DADADADA0 DADA0DADADADADADADADADA ;DADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0######### ;######## ####ddh</t>
+    <t>DADADADA0 DADA0DADADADADADADADADA ;DADADADADADADADA DADADADADDHA</t>
   </si>
   <si>
-    <t>#### ####0 ##0######### #### ##0.1</t>
+    <t>DADADADA DADADADA0 DADA0DADADADADADADADADA DADADADA DADA0.1</t>
   </si>
   <si>
-    <t>#### ####0 ##0######### #### ##0.2</t>
+    <t>DADADADA DADADADA0 DADA0DADADADADADADADADA DADADADA DADA0.2</t>
   </si>
   <si>
-    <t>##### ##### #####e ######### #### ##0.1</t>
+    <t>DADADADADA DADADADADA DADADADADAE DADADADADADADADADA DADADADA DADA0.1</t>
   </si>
   <si>
-    <t>##### ##### #####e ######### #### ##0.2</t>
+    <t>DADADADADA DADADADADA DADADADADAE DADADADADADADADADA DADADADA DADA0.2</t>
   </si>
   <si>
-    <t>##### ##### #####e ######### #### ##0.3</t>
+    <t>DADADADADA DADADADADA DADADADADAE DADADADADADADADADA DADADADA DADA0.3</t>
   </si>
   <si>
-    <t>##0 ##0 ##0##### ;#0##0ddh</t>
+    <t>DADA0 DADA0 DADA0DADADADADA ;DA0DADA0DDHA</t>
   </si>
   <si>
-    <t>#### ####0 ##0 #### #### ##0.1</t>
+    <t>DADADADA DADADADA0 DADA0 DADADADA DADADADA DADA0.1</t>
   </si>
   <si>
-    <t>#### ####0 ##0 #### #### ##0.2</t>
+    <t>DADADADA DADADADA0 DADA0 DADADADA DADADADA DADA0.2</t>
   </si>
   <si>
-    <t>#### ####0 ##0########</t>
+    <t>DADADADA DADADADA0 DADA0DADADADADADADADA</t>
   </si>
   <si>
-    <t>####0##0######## ##### ##### #####</t>
+    <t>DADADADA0DADA0DADADADADADADADA DADADADADA DADADADADA DADADADADA</t>
   </si>
   <si>
-    <t>####0 ##0###;###0##0ddh</t>
+    <t>DADADADA0 DADA0DADADA;DADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0###;####0##0ddh</t>
+    <t>DADADADA0 DADA0DADADA;DADADADA0DADA0DDHA</t>
   </si>
   <si>
-    <t>####0 ##0e ######e #0##0.#</t>
+    <t>DADADADA0 DADA0E DADADADADADAE DA0DADA0.DA</t>
   </si>
   <si>
-    <t>####0 ##0#####</t>
+    <t>DADADADA0 DADA0DADADADADA</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -740,8 +809,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -757,7 +834,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -765,12 +842,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1069,82 +1164,151 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:24">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D2" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="E2" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="F2" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="G2" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="H2" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="I2" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="J2" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="K2" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="L2" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="M2" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="N2" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="O2" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="P2" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="Q2" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="R2" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="S2" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="T2" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="U2" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="V2" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="W2" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="X2" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -1152,7 +1316,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>1042</v>
@@ -1226,7 +1390,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>1156</v>
@@ -1300,7 +1464,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>1075</v>
@@ -1374,7 +1538,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>1023</v>
@@ -1448,7 +1612,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>847</v>
@@ -1522,7 +1686,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>1169</v>
@@ -1596,7 +1760,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>1176</v>
@@ -1670,7 +1834,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C10">
         <v>1120</v>
@@ -1744,7 +1908,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C11">
         <v>1105</v>
@@ -1818,7 +1982,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C12">
         <v>1032</v>
@@ -1892,7 +2056,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C13">
         <v>1001</v>
@@ -1966,7 +2130,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C14">
         <v>983</v>
@@ -2040,7 +2204,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C15">
         <v>1096</v>
@@ -2114,7 +2278,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C16">
         <v>1071</v>
@@ -2188,7 +2352,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C17">
         <v>999</v>
@@ -2262,7 +2426,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C18">
         <v>1216</v>
@@ -2336,7 +2500,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C19">
         <v>1081</v>
@@ -2410,7 +2574,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C20">
         <v>1160</v>
@@ -2484,7 +2648,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C21">
         <v>1083</v>
@@ -2558,7 +2722,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C22">
         <v>893</v>
@@ -2632,7 +2796,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C23">
         <v>1025</v>
@@ -2706,7 +2870,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C24">
         <v>1049</v>
@@ -2780,7 +2944,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C25">
         <v>1053</v>
@@ -2854,7 +3018,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C26">
         <v>1136</v>
@@ -2928,7 +3092,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C27">
         <v>1207</v>
@@ -3002,7 +3166,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C28">
         <v>1133</v>
@@ -3076,7 +3240,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C29">
         <v>1212</v>
@@ -3150,7 +3314,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C30">
         <v>1155</v>
@@ -3224,7 +3388,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>1215</v>
@@ -3298,7 +3462,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>1037</v>
@@ -3372,7 +3536,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>917</v>
@@ -3446,7 +3610,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C34">
         <v>758</v>
@@ -3520,7 +3684,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>695</v>
@@ -3594,7 +3758,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C36">
         <v>776</v>
@@ -3668,7 +3832,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>796</v>
@@ -3742,7 +3906,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C38">
         <v>1117</v>
@@ -3816,7 +3980,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C39">
         <v>978</v>
@@ -3890,7 +4054,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C40">
         <v>936</v>
@@ -3964,7 +4128,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C41">
         <v>1061</v>
@@ -4038,7 +4202,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C42">
         <v>1103</v>
@@ -4112,7 +4276,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C43">
         <v>1071</v>
@@ -4186,7 +4350,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C44">
         <v>833</v>
@@ -4260,7 +4424,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C45">
         <v>955</v>
@@ -4334,7 +4498,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C46">
         <v>962</v>
@@ -4408,7 +4572,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C47">
         <v>846</v>
@@ -4482,7 +4646,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C48">
         <v>1046</v>
@@ -4556,7 +4720,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C49">
         <v>1011</v>
@@ -4630,7 +4794,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C50">
         <v>657</v>
@@ -4704,7 +4868,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C51">
         <v>608</v>
@@ -4778,7 +4942,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C52">
         <v>1127</v>
@@ -4852,7 +5016,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>1146</v>
@@ -4926,7 +5090,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C54">
         <v>899</v>
@@ -5000,7 +5164,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C55">
         <v>671</v>
@@ -5074,7 +5238,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="C56">
         <v>1134</v>
@@ -5148,7 +5312,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C57">
         <v>1125</v>
@@ -5222,7 +5386,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="C58">
         <v>858</v>
@@ -5296,7 +5460,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C59">
         <v>280</v>
@@ -5370,7 +5534,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C60">
         <v>1092</v>
@@ -5444,7 +5608,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C61">
         <v>1094</v>
@@ -5518,7 +5682,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C62">
         <v>1090</v>
@@ -5592,7 +5756,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C63">
         <v>1091</v>
@@ -5666,7 +5830,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C64">
         <v>1098</v>
@@ -5740,7 +5904,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C65">
         <v>573</v>
@@ -5814,7 +5978,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C66">
         <v>638</v>
@@ -5888,7 +6052,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C67">
         <v>882</v>
@@ -5962,7 +6126,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C68">
         <v>1121</v>
@@ -6036,7 +6200,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C69">
         <v>861</v>
@@ -6110,7 +6274,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C70">
         <v>852</v>
@@ -6184,7 +6348,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C71">
         <v>967</v>
@@ -6258,7 +6422,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="C72">
         <v>781</v>
@@ -6332,7 +6496,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="C73">
         <v>775</v>
@@ -6406,7 +6570,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="C74">
         <v>928</v>
@@ -6480,7 +6644,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="C75">
         <v>1105</v>
@@ -6554,7 +6718,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="C76">
         <v>1124</v>
@@ -6628,7 +6792,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C77">
         <v>1044</v>
@@ -6702,7 +6866,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C78">
         <v>1130</v>
@@ -6776,7 +6940,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C79">
         <v>1101</v>
@@ -6850,7 +7014,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C80">
         <v>1064</v>
@@ -6924,7 +7088,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C81">
         <v>1032</v>
@@ -6998,7 +7162,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C82">
         <v>820</v>
@@ -7072,7 +7236,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="C83">
         <v>649</v>
@@ -7146,7 +7310,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C84">
         <v>1142</v>
@@ -7220,7 +7384,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C85">
         <v>1169</v>
@@ -7294,7 +7458,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C86">
         <v>1139</v>
@@ -7368,7 +7532,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C87">
         <v>1135</v>
@@ -7442,7 +7606,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="C88">
         <v>1073</v>
@@ -7516,7 +7680,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="C89">
         <v>733</v>
@@ -7590,7 +7754,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="C90">
         <v>998</v>
@@ -7664,7 +7828,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C91">
         <v>1054</v>
@@ -7738,7 +7902,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="C92">
         <v>1075</v>
@@ -7812,7 +7976,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C93">
         <v>944</v>
@@ -7886,7 +8050,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C94">
         <v>1009</v>
@@ -7960,7 +8124,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="C95">
         <v>726</v>
@@ -8034,7 +8198,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="C96">
         <v>710</v>
@@ -8108,7 +8272,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="C97">
         <v>826</v>
@@ -8182,7 +8346,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="C98">
         <v>831</v>
@@ -8256,7 +8420,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C99">
         <v>1097</v>
@@ -8330,7 +8494,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C100">
         <v>403</v>
@@ -8404,7 +8568,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="C101">
         <v>721</v>
@@ -8478,7 +8642,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="C102">
         <v>477</v>
@@ -8552,7 +8716,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C103">
         <v>881</v>
@@ -8626,7 +8790,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C104">
         <v>298</v>
@@ -8700,7 +8864,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C105">
         <v>900</v>
@@ -8774,7 +8938,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="C106">
         <v>846</v>
@@ -8848,7 +9012,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="C107">
         <v>869</v>
@@ -8922,7 +9086,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C108">
         <v>543</v>
@@ -8996,7 +9160,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="C109">
         <v>985</v>
@@ -9070,7 +9234,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C110">
         <v>634</v>
@@ -9144,7 +9308,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="C111">
         <v>856</v>
@@ -9218,7 +9382,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C112">
         <v>583</v>
@@ -9292,7 +9456,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="C113">
         <v>629</v>
@@ -9366,7 +9530,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="C114">
         <v>650</v>
@@ -9440,7 +9604,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C115">
         <v>754</v>
@@ -9514,7 +9678,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C116">
         <v>267</v>
@@ -9588,7 +9752,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C117">
         <v>704</v>
@@ -9662,7 +9826,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="C118">
         <v>597</v>
@@ -9736,7 +9900,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C119">
         <v>626</v>
@@ -9810,7 +9974,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="C120">
         <v>1044</v>
@@ -9884,7 +10048,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="C121">
         <v>1080</v>
@@ -9958,7 +10122,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C122">
         <v>1054</v>
@@ -10032,7 +10196,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C123">
         <v>896</v>
@@ -10106,7 +10270,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="C124">
         <v>764</v>
@@ -10180,7 +10344,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="C125">
         <v>780</v>
@@ -10254,7 +10418,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C126">
         <v>1042</v>
@@ -10328,7 +10492,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C127">
         <v>864</v>
@@ -10402,7 +10566,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C128">
         <v>795</v>
@@ -10476,7 +10640,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="C129">
         <v>944</v>
@@ -10550,7 +10714,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C130">
         <v>1017</v>
@@ -10624,7 +10788,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="C131">
         <v>993</v>
@@ -10698,7 +10862,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="C132">
         <v>1005</v>
@@ -10772,7 +10936,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C133">
         <v>701</v>
@@ -10846,7 +11010,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="C134">
         <v>330</v>
@@ -10920,7 +11084,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="C135">
         <v>836</v>
@@ -10994,7 +11158,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="C136">
         <v>729</v>
@@ -11068,7 +11232,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C137">
         <v>1139</v>
@@ -11142,7 +11306,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C138">
         <v>946</v>
@@ -11216,7 +11380,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C139">
         <v>974</v>
@@ -11290,7 +11454,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="C140">
         <v>861</v>
@@ -11364,7 +11528,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="C141">
         <v>692</v>
@@ -11438,7 +11602,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="C142">
         <v>1122</v>
@@ -11512,7 +11676,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="C143">
         <v>761</v>
@@ -11586,7 +11750,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="C144">
         <v>784</v>
@@ -11660,7 +11824,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="C145">
         <v>963</v>
@@ -11734,7 +11898,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="C146">
         <v>1006</v>
@@ -11808,7 +11972,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="C147">
         <v>669</v>
@@ -11882,7 +12046,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="C148">
         <v>679</v>
@@ -11956,7 +12120,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="C149">
         <v>1042</v>
@@ -12030,7 +12194,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="C150">
         <v>901</v>
@@ -12104,7 +12268,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C151">
         <v>1153</v>
@@ -12178,7 +12342,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C152">
         <v>803</v>
@@ -12252,7 +12416,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C153">
         <v>825</v>
@@ -12326,7 +12490,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C154">
         <v>1138</v>
@@ -12400,7 +12564,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="C155">
         <v>886</v>
@@ -12474,7 +12638,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="C156">
         <v>1079</v>
@@ -12548,7 +12712,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="C157">
         <v>814</v>
@@ -12622,7 +12786,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="C158">
         <v>959</v>
@@ -12696,7 +12860,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C159">
         <v>755</v>
@@ -12770,7 +12934,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C160">
         <v>972</v>
@@ -12844,7 +13008,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C161">
         <v>1088</v>
@@ -12918,7 +13082,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C162">
         <v>1087</v>
@@ -12992,7 +13156,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C163">
         <v>1000</v>
@@ -13066,7 +13230,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C164">
         <v>811</v>
@@ -13140,7 +13304,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="C165">
         <v>792</v>
@@ -13214,7 +13378,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="C166">
         <v>624</v>
@@ -13288,7 +13452,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="C167">
         <v>691</v>
@@ -13362,7 +13526,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C168">
         <v>904</v>
@@ -13436,7 +13600,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="C169">
         <v>982</v>
@@ -13510,7 +13674,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="C170">
         <v>872</v>
@@ -13584,7 +13748,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="C171">
         <v>900</v>
@@ -13658,7 +13822,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C172">
         <v>820</v>
@@ -13732,7 +13896,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="C173">
         <v>894</v>
@@ -13806,7 +13970,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="C174">
         <v>915</v>
@@ -13880,7 +14044,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="C175">
         <v>891</v>
@@ -13954,7 +14118,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="C176">
         <v>1080</v>
@@ -14028,7 +14192,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="C177">
         <v>920</v>
@@ -14102,7 +14266,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="C178">
         <v>896</v>
@@ -14176,7 +14340,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="C179">
         <v>876</v>
@@ -14250,7 +14414,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="C180">
         <v>1011</v>
@@ -14324,7 +14488,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="C181">
         <v>837</v>
@@ -14398,7 +14562,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="C182">
         <v>623</v>
@@ -14472,7 +14636,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="C183">
         <v>575</v>
@@ -14546,7 +14710,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="C184">
         <v>650</v>
@@ -14620,7 +14784,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="C185">
         <v>595</v>
@@ -14694,7 +14858,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="C186">
         <v>626</v>
@@ -14768,7 +14932,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="C187">
         <v>517</v>
@@ -14842,7 +15006,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="C188">
         <v>596</v>
@@ -14916,7 +15080,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="C189">
         <v>640</v>
@@ -14990,7 +15154,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="C190">
         <v>794</v>
@@ -15064,7 +15228,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="C191">
         <v>741</v>
@@ -15138,7 +15302,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="C192">
         <v>779</v>
@@ -15212,7 +15376,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C193">
         <v>805</v>
@@ -15286,7 +15450,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="C194">
         <v>866</v>
@@ -15360,7 +15524,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="C195">
         <v>721</v>
@@ -15434,7 +15598,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="C196">
         <v>816</v>
@@ -15508,7 +15672,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="C197">
         <v>762</v>
@@ -15582,7 +15746,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="C198">
         <v>920</v>
@@ -15656,7 +15820,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="C199">
         <v>929</v>
@@ -15730,7 +15894,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="C200">
         <v>403</v>
@@ -15804,7 +15968,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="C201">
         <v>558</v>
@@ -15878,7 +16042,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C202">
         <v>406</v>
@@ -15952,7 +16116,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="C203">
         <v>1144</v>
@@ -16026,7 +16190,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="C204">
         <v>847</v>
@@ -16100,7 +16264,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C205">
         <v>575</v>
@@ -16174,7 +16338,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="C206">
         <v>564</v>
@@ -16248,7 +16412,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C207">
         <v>586</v>
@@ -16322,7 +16486,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C208">
         <v>499</v>
@@ -16396,7 +16560,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="C209">
         <v>852</v>
@@ -16470,7 +16634,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="C210">
         <v>807</v>
@@ -16544,7 +16708,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="C211">
         <v>648</v>
@@ -16618,7 +16782,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="C212">
         <v>656</v>
@@ -16692,7 +16856,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C213">
         <v>842</v>
@@ -16766,7 +16930,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="C214">
         <v>1085</v>
@@ -16840,7 +17004,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="C215">
         <v>1145</v>
@@ -16914,7 +17078,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C216">
         <v>561</v>
@@ -16988,7 +17152,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="C217">
         <v>929</v>
@@ -17062,7 +17226,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="C218">
         <v>955</v>
@@ -17136,7 +17300,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="C219">
         <v>1064</v>
@@ -17210,7 +17374,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C220">
         <v>397</v>
@@ -17284,7 +17448,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C221">
         <v>1140</v>
@@ -17358,7 +17522,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="C222">
         <v>986</v>
@@ -17432,7 +17596,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="C223">
         <v>1000</v>
@@ -17506,7 +17670,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="C224">
         <v>922</v>
@@ -17580,7 +17744,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C225">
         <v>1110</v>
@@ -17654,7 +17818,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="C226">
         <v>848</v>
@@ -17728,7 +17892,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="C227">
         <v>717</v>
@@ -17802,7 +17966,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="C228">
         <v>718</v>
@@ -17876,7 +18040,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C229">
         <v>733</v>
@@ -17950,7 +18114,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="C230">
         <v>1013</v>
@@ -18024,7 +18188,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C231">
         <v>1079</v>
@@ -18098,7 +18262,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C232">
         <v>588</v>
@@ -18172,7 +18336,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C233">
         <v>448</v>
@@ -18246,7 +18410,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="C234">
         <v>983</v>
@@ -18320,7 +18484,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="C235">
         <v>990</v>
@@ -18394,7 +18558,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="C236">
         <v>638</v>
@@ -18468,7 +18632,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="C237">
         <v>784</v>
@@ -18542,7 +18706,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="C238">
         <v>990</v>
@@ -18616,7 +18780,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="C239">
         <v>821</v>
@@ -18690,7 +18854,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="C240">
         <v>834</v>
@@ -18764,7 +18928,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="C241">
         <v>952</v>
@@ -18838,7 +19002,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C242">
         <v>413</v>
@@ -18912,7 +19076,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C243">
         <v>909</v>
@@ -18986,7 +19150,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C244">
         <v>922</v>
@@ -19060,7 +19224,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="C245">
         <v>1102</v>
@@ -19134,7 +19298,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="C246">
         <v>1206</v>
@@ -19208,7 +19372,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C247">
         <v>973</v>
@@ -19282,7 +19446,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C248">
         <v>1041</v>
@@ -19356,7 +19520,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="C249">
         <v>1003</v>
@@ -19430,7 +19594,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="C250">
         <v>1000</v>
@@ -19504,7 +19668,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="C251">
         <v>1032</v>
@@ -19578,7 +19742,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="C252">
         <v>871</v>
@@ -19652,7 +19816,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="C253">
         <v>969</v>
@@ -19726,7 +19890,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="C254">
         <v>1040</v>
@@ -19800,7 +19964,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="C255">
         <v>1124</v>
@@ -19874,7 +20038,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="C256">
         <v>969</v>
@@ -19948,7 +20112,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C257">
         <v>889</v>
@@ -20022,7 +20186,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="C258">
         <v>1045</v>
@@ -20096,7 +20260,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C259">
         <v>507</v>
@@ -20170,7 +20334,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="C260">
         <v>947</v>
@@ -20244,7 +20408,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="C261">
         <v>930</v>
@@ -20318,7 +20482,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="C262">
         <v>826</v>
@@ -20392,7 +20556,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="C263">
         <v>807</v>
@@ -20466,7 +20630,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="C264">
         <v>1102</v>
@@ -20540,7 +20704,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="C265">
         <v>1109</v>
@@ -20614,7 +20778,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="C266">
         <v>966</v>
@@ -20688,7 +20852,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="C267">
         <v>775</v>
@@ -20762,7 +20926,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="C268">
         <v>848</v>
@@ -20836,7 +21000,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="C269">
         <v>1168</v>
@@ -20910,7 +21074,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="C270">
         <v>1066</v>
@@ -20984,7 +21148,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="C271">
         <v>1017</v>
@@ -21058,7 +21222,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="C272">
         <v>1000</v>
@@ -21132,7 +21296,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="C273">
         <v>961</v>
@@ -21206,7 +21370,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="C274">
         <v>641</v>
@@ -21280,7 +21444,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="C275">
         <v>671</v>
@@ -21354,7 +21518,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="C276">
         <v>956</v>
@@ -21428,7 +21592,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="C277">
         <v>914</v>
@@ -21502,7 +21666,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="C278">
         <v>847</v>
@@ -21576,7 +21740,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C279">
         <v>711</v>
@@ -21650,7 +21814,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="C280">
         <v>840</v>
@@ -21724,7 +21888,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="C281">
         <v>888</v>
@@ -21798,7 +21962,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="C282">
         <v>819</v>
@@ -21872,7 +22036,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C283">
         <v>844</v>
@@ -21946,7 +22110,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="C284">
         <v>893</v>
@@ -22020,7 +22184,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="C285">
         <v>803</v>
@@ -22094,7 +22258,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="C286">
         <v>764</v>
@@ -22168,7 +22332,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="C287">
         <v>1072</v>
@@ -22242,7 +22406,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C288">
         <v>504</v>
@@ -22316,7 +22480,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C289">
         <v>704</v>
@@ -22390,7 +22554,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C290">
         <v>983</v>
@@ -22464,7 +22628,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="C291">
         <v>1154</v>
@@ -22538,7 +22702,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="C292">
         <v>815</v>
@@ -22612,7 +22776,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="C293">
         <v>824</v>
@@ -22686,7 +22850,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="C294">
         <v>738</v>
@@ -22760,7 +22924,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="C295">
         <v>921</v>
@@ -22834,7 +22998,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="C296">
         <v>868</v>
@@ -22908,7 +23072,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="C297">
         <v>775</v>
@@ -22982,7 +23146,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="C298">
         <v>918</v>
@@ -23056,7 +23220,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="C299">
         <v>971</v>
@@ -23130,7 +23294,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="C300">
         <v>973</v>
@@ -23204,7 +23368,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="C301">
         <v>1056</v>
@@ -23278,7 +23442,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="C302">
         <v>777</v>
@@ -23352,7 +23516,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="C303">
         <v>787</v>
@@ -23426,7 +23590,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C304">
         <v>581</v>
@@ -23500,7 +23664,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="C305">
         <v>734</v>
@@ -23574,7 +23738,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="C306">
         <v>765</v>
@@ -23648,7 +23812,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="C307">
         <v>818</v>
@@ -23722,7 +23886,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="C308">
         <v>816</v>
@@ -23796,7 +23960,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="C309">
         <v>874</v>
@@ -23870,7 +24034,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="C310">
         <v>927</v>
@@ -23944,7 +24108,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="C311">
         <v>1068</v>
@@ -24018,7 +24182,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="C312">
         <v>992</v>
@@ -24092,7 +24256,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="C313">
         <v>813</v>
@@ -24166,7 +24330,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="C314">
         <v>844</v>
@@ -24240,7 +24404,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C315">
         <v>730</v>
@@ -24314,7 +24478,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="C316">
         <v>986</v>
@@ -24388,7 +24552,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="C317">
         <v>484</v>
@@ -24462,7 +24626,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C318">
         <v>460</v>
@@ -24536,7 +24700,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C319">
         <v>473</v>
@@ -24610,7 +24774,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C320">
         <v>884</v>
@@ -24684,7 +24848,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="C321">
         <v>484</v>
@@ -24758,7 +24922,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C322">
         <v>470</v>
@@ -24832,7 +24996,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="C323">
         <v>207</v>
@@ -24906,7 +25070,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C324">
         <v>175</v>
@@ -24980,7 +25144,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C325">
         <v>600</v>
@@ -25054,7 +25218,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C326">
         <v>608</v>
@@ -25128,7 +25292,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C327">
         <v>675</v>
@@ -25202,7 +25366,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C328">
         <v>501</v>
@@ -25276,7 +25440,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C329">
         <v>302</v>
@@ -25350,7 +25514,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="C330">
         <v>680</v>
@@ -25424,7 +25588,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="C331">
         <v>540</v>
@@ -25498,7 +25662,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="C332">
         <v>820</v>
@@ -25572,7 +25736,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="C333">
         <v>624</v>
@@ -25646,7 +25810,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="C334">
         <v>1050</v>
@@ -25720,7 +25884,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="C335">
         <v>985</v>
@@ -25794,7 +25958,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="C336">
         <v>932</v>
@@ -25868,7 +26032,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="C337">
         <v>1012</v>
@@ -25942,7 +26106,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="C338">
         <v>931</v>
@@ -26016,7 +26180,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="C339">
         <v>905</v>
@@ -26090,7 +26254,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="C340">
         <v>709</v>
@@ -26164,7 +26328,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="C341">
         <v>1132</v>
@@ -26238,7 +26402,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C342">
         <v>1190</v>
@@ -26312,7 +26476,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C343">
         <v>711</v>
@@ -26386,7 +26550,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C344">
         <v>1158</v>
@@ -26460,7 +26624,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="C345">
         <v>1113</v>
@@ -26534,7 +26698,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="C346">
         <v>1021</v>
@@ -26608,7 +26772,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="C347">
         <v>968</v>
@@ -26682,7 +26846,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="C348">
         <v>1148</v>
@@ -26756,7 +26920,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="C349">
         <v>1149</v>
@@ -26830,7 +26994,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="C350">
         <v>610</v>
@@ -26904,7 +27068,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="C351">
         <v>683</v>
@@ -26978,7 +27142,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="C352">
         <v>1036</v>
@@ -27052,7 +27216,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="C353">
         <v>1003</v>
@@ -27126,7 +27290,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="C354">
         <v>891</v>
@@ -27200,7 +27364,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C355">
         <v>971</v>
@@ -27274,7 +27438,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="C356">
         <v>888</v>
@@ -27348,7 +27512,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="C357">
         <v>904</v>
@@ -27422,7 +27586,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="C358">
         <v>905</v>
@@ -27496,7 +27660,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="C359">
         <v>1185</v>
@@ -27570,7 +27734,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="C360">
         <v>1101</v>
@@ -27644,7 +27808,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="C361">
         <v>1062</v>
@@ -27718,7 +27882,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C362">
         <v>407</v>
@@ -27792,7 +27956,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="C363">
         <v>899</v>
@@ -27866,7 +28030,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="C364">
         <v>806</v>
@@ -27940,7 +28104,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="C365">
         <v>876</v>
@@ -28014,7 +28178,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="C366">
         <v>612</v>
@@ -28088,7 +28252,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="C367">
         <v>648</v>
@@ -28162,7 +28326,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="C368">
         <v>637</v>
@@ -28236,7 +28400,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="C369">
         <v>641</v>
@@ -28310,7 +28474,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C370">
         <v>738</v>
@@ -28384,7 +28548,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C371">
         <v>733</v>
@@ -28458,7 +28622,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="C372">
         <v>1104</v>
@@ -28532,7 +28696,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="C373">
         <v>799</v>
@@ -28606,7 +28770,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C374">
         <v>957</v>
@@ -28680,7 +28844,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="C375">
         <v>930</v>
@@ -28754,7 +28918,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="C376">
         <v>799</v>
@@ -28828,7 +28992,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="C377">
         <v>483</v>
@@ -28902,7 +29066,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="C378">
         <v>810</v>
@@ -28976,7 +29140,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="C379">
         <v>1131</v>
@@ -29050,7 +29214,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="C380">
         <v>794</v>
@@ -29124,7 +29288,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C381">
         <v>810</v>
@@ -29198,7 +29362,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C382">
         <v>710</v>
@@ -29272,7 +29436,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="C383">
         <v>394</v>
@@ -29346,7 +29510,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C384">
         <v>788</v>
